--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
@@ -2597,11 +2597,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75178741"/>
-        <c:axId val="4188506"/>
+        <c:axId val="85834260"/>
+        <c:axId val="50073575"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="75178741"/>
+        <c:axId val="85834260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2635,7 +2635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4188506"/>
+        <c:crossAx val="50073575"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2647,7 +2647,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="4188506"/>
+        <c:axId val="50073575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2690,7 +2690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75178741"/>
+        <c:crossAx val="85834260"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3257,7 +3257,7 @@
                   <c:v>105.417091487533</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>78.6028988674357</c:v>
+                  <c:v>79.7298217687948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3272,11 +3272,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="388860"/>
-        <c:axId val="23151715"/>
+        <c:axId val="68339772"/>
+        <c:axId val="90153863"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="388860"/>
+        <c:axId val="68339772"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3308,14 +3308,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23151715"/>
+        <c:crossAx val="90153863"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="23151715"/>
+        <c:axId val="90153863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3389,7 +3389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="388860"/>
+        <c:crossAx val="68339772"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7392,7 +7392,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -7944,23 +7944,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -11511,7 +11511,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15640,15 +15640,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>78.6028988674357</v>
+        <v>79.7298217687948</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -15775,15 +15775,15 @@
       </c>
       <c r="T2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="83" t="n">
         <f aca="false">+Q33</f>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="X2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="H39" s="89" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="89"/>
       <c r="J39" s="89"/>
@@ -17000,7 +17000,7 @@
       <c r="P39" s="89"/>
       <c r="Q39" s="89" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
@@ -2597,11 +2597,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="85834260"/>
-        <c:axId val="50073575"/>
+        <c:axId val="16817400"/>
+        <c:axId val="64157941"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="85834260"/>
+        <c:axId val="16817400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2635,7 +2635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50073575"/>
+        <c:crossAx val="64157941"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2647,7 +2647,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="50073575"/>
+        <c:axId val="64157941"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2690,7 +2690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85834260"/>
+        <c:crossAx val="16817400"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3272,11 +3272,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="68339772"/>
-        <c:axId val="90153863"/>
+        <c:axId val="7019740"/>
+        <c:axId val="87896243"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="68339772"/>
+        <c:axId val="7019740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3308,14 +3308,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90153863"/>
+        <c:crossAx val="87896243"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90153863"/>
+        <c:axId val="87896243"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3389,7 +3389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68339772"/>
+        <c:crossAx val="7019740"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
@@ -2597,11 +2597,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16817400"/>
-        <c:axId val="64157941"/>
+        <c:axId val="70684292"/>
+        <c:axId val="38199591"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="16817400"/>
+        <c:axId val="70684292"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2635,7 +2635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64157941"/>
+        <c:crossAx val="38199591"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2647,7 +2647,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="64157941"/>
+        <c:axId val="38199591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2690,7 +2690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16817400"/>
+        <c:crossAx val="70684292"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3272,11 +3272,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="7019740"/>
-        <c:axId val="87896243"/>
+        <c:axId val="39573432"/>
+        <c:axId val="85700335"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="7019740"/>
+        <c:axId val="39573432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3308,14 +3308,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87896243"/>
+        <c:crossAx val="85700335"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="87896243"/>
+        <c:axId val="85700335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3389,7 +3389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7019740"/>
+        <c:crossAx val="39573432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORRIENTE.xlsx
@@ -2597,11 +2597,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="70684292"/>
-        <c:axId val="38199591"/>
+        <c:axId val="63568380"/>
+        <c:axId val="31788835"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70684292"/>
+        <c:axId val="63568380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2635,7 +2635,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38199591"/>
+        <c:crossAx val="31788835"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2647,7 +2647,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="38199591"/>
+        <c:axId val="31788835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2690,7 +2690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70684292"/>
+        <c:crossAx val="63568380"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3272,11 +3272,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="39573432"/>
-        <c:axId val="85700335"/>
+        <c:axId val="15212556"/>
+        <c:axId val="52793967"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="39573432"/>
+        <c:axId val="15212556"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3308,14 +3308,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85700335"/>
+        <c:crossAx val="52793967"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="85700335"/>
+        <c:axId val="52793967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3389,7 +3389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39573432"/>
+        <c:crossAx val="15212556"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
